--- a/rcads/data/xls/24_Sections.xlsx
+++ b/rcads/data/xls/24_Sections.xlsx
@@ -393,6 +393,11 @@
       <c r="D2" s="0">
         <v>171</v>
       </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="3">
       <c r="A3" s="0">
@@ -409,6 +414,11 @@
       <c r="D3" s="0">
         <v>172</v>
       </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="4">
       <c r="A4" s="0">
@@ -425,6 +435,11 @@
       <c r="D4" s="0">
         <v>173</v>
       </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="5">
       <c r="A5" s="0">
@@ -441,6 +456,11 @@
       <c r="D5" s="0">
         <v>174</v>
       </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="6">
       <c r="A6" s="0">
@@ -457,6 +477,11 @@
       <c r="D6" s="0">
         <v>175</v>
       </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="7">
       <c r="A7" s="0">
@@ -473,6 +498,11 @@
       <c r="D7" s="0">
         <v>176</v>
       </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="8">
       <c r="A8" s="0">
@@ -489,6 +519,11 @@
       <c r="D8" s="0">
         <v>177</v>
       </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="9">
       <c r="A9" s="0">
@@ -505,6 +540,11 @@
       <c r="D9" s="0">
         <v>178</v>
       </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="10">
       <c r="A10" s="0">
@@ -521,6 +561,11 @@
       <c r="D10" s="0">
         <v>168</v>
       </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="11">
       <c r="A11" s="0">
@@ -537,6 +582,11 @@
       <c r="D11" s="0">
         <v>169</v>
       </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="12">
       <c r="A12" s="0">
@@ -553,6 +603,11 @@
       <c r="D12" s="0">
         <v>170</v>
       </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="13">
       <c r="A13" s="0">
@@ -569,6 +624,11 @@
       <c r="D13" s="0">
         <v>171</v>
       </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="14">
       <c r="A14" s="0">
@@ -585,6 +645,11 @@
       <c r="D14" s="0">
         <v>172</v>
       </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="15">
       <c r="A15" s="0">
@@ -601,6 +666,11 @@
       <c r="D15" s="0">
         <v>173</v>
       </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="16">
       <c r="A16" s="0">
@@ -617,6 +687,11 @@
       <c r="D16" s="0">
         <v>174</v>
       </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="17">
       <c r="A17" s="0">
@@ -633,6 +708,11 @@
       <c r="D17" s="0">
         <v>175</v>
       </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="18">
       <c r="A18" s="0">
@@ -649,6 +729,11 @@
       <c r="D18" s="0">
         <v>176</v>
       </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="19">
       <c r="A19" s="0">
@@ -665,6 +750,11 @@
       <c r="D19" s="0">
         <v>177</v>
       </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="20">
       <c r="A20" s="0">
@@ -681,6 +771,11 @@
       <c r="D20" s="0">
         <v>178</v>
       </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="21">
       <c r="A21" s="0">
@@ -697,6 +792,11 @@
       <c r="D21" s="0">
         <v>168</v>
       </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="22">
       <c r="A22" s="0">
@@ -713,6 +813,11 @@
       <c r="D22" s="0">
         <v>169</v>
       </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="23">
       <c r="A23" s="0">
@@ -729,6 +834,11 @@
       <c r="D23" s="0">
         <v>170</v>
       </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="24">
       <c r="A24" s="0">
@@ -745,6 +855,11 @@
       <c r="D24" s="0">
         <v>171</v>
       </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="25">
       <c r="A25" s="0">
@@ -761,6 +876,11 @@
       <c r="D25" s="0">
         <v>172</v>
       </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="26">
       <c r="A26" s="0">
@@ -777,6 +897,11 @@
       <c r="D26" s="0">
         <v>173</v>
       </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="27">
       <c r="A27" s="0">
@@ -793,6 +918,11 @@
       <c r="D27" s="0">
         <v>174</v>
       </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="28">
       <c r="A28" s="0">
@@ -809,6 +939,11 @@
       <c r="D28" s="0">
         <v>175</v>
       </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="29">
       <c r="A29" s="0">
@@ -825,6 +960,11 @@
       <c r="D29" s="0">
         <v>176</v>
       </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="30">
       <c r="A30" s="0">
@@ -841,6 +981,11 @@
       <c r="D30" s="0">
         <v>177</v>
       </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="31">
       <c r="A31" s="0">
@@ -857,6 +1002,11 @@
       <c r="D31" s="0">
         <v>178</v>
       </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="32">
       <c r="A32" s="0">
@@ -4001,6 +4151,11 @@
       <c r="D244" s="0">
         <v>168</v>
       </c>
+      <c r="E244" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="245">
       <c r="A245" s="0">
@@ -4017,6 +4172,11 @@
       <c r="D245" s="0">
         <v>169</v>
       </c>
+      <c r="E245" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="246">
       <c r="A246" s="0">
@@ -4033,6 +4193,11 @@
       <c r="D246" s="0">
         <v>170</v>
       </c>
+      <c r="E246" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="247">
       <c r="A247" s="0">
@@ -4049,6 +4214,11 @@
       <c r="D247" s="0">
         <v>171</v>
       </c>
+      <c r="E247" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="248">
       <c r="A248" s="0">
@@ -4065,6 +4235,11 @@
       <c r="D248" s="0">
         <v>172</v>
       </c>
+      <c r="E248" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="249">
       <c r="A249" s="0">
@@ -4081,6 +4256,11 @@
       <c r="D249" s="0">
         <v>173</v>
       </c>
+      <c r="E249" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="250">
       <c r="A250" s="0">
@@ -4097,6 +4277,11 @@
       <c r="D250" s="0">
         <v>174</v>
       </c>
+      <c r="E250" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="251">
       <c r="A251" s="0">
@@ -4113,6 +4298,11 @@
       <c r="D251" s="0">
         <v>175</v>
       </c>
+      <c r="E251" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="252">
       <c r="A252" s="0">
@@ -4129,6 +4319,11 @@
       <c r="D252" s="0">
         <v>176</v>
       </c>
+      <c r="E252" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="253">
       <c r="A253" s="0">
@@ -4145,6 +4340,11 @@
       <c r="D253" s="0">
         <v>177</v>
       </c>
+      <c r="E253" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="254">
       <c r="A254" s="0">
@@ -4161,6 +4361,11 @@
       <c r="D254" s="0">
         <v>178</v>
       </c>
+      <c r="E254" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="255">
       <c r="A255" s="0">
@@ -4177,6 +4382,11 @@
       <c r="D255" s="0">
         <v>168</v>
       </c>
+      <c r="E255" s="0" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="256">
       <c r="A256" s="0">
@@ -4193,6 +4403,11 @@
       <c r="D256" s="0">
         <v>169</v>
       </c>
+      <c r="E256" s="0" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="257">
       <c r="A257" s="0">
@@ -4209,6 +4424,11 @@
       <c r="D257" s="0">
         <v>170</v>
       </c>
+      <c r="E257" s="0" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="258">
       <c r="A258" s="0">
@@ -4225,6 +4445,11 @@
       <c r="D258" s="0">
         <v>171</v>
       </c>
+      <c r="E258" s="0" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="259">
       <c r="A259" s="0">
@@ -4241,6 +4466,11 @@
       <c r="D259" s="0">
         <v>172</v>
       </c>
+      <c r="E259" s="0" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="260">
       <c r="A260" s="0">
@@ -4257,6 +4487,11 @@
       <c r="D260" s="0">
         <v>173</v>
       </c>
+      <c r="E260" s="0" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="261">
       <c r="A261" s="0">
@@ -4273,6 +4508,11 @@
       <c r="D261" s="0">
         <v>174</v>
       </c>
+      <c r="E261" s="0" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="262">
       <c r="A262" s="0">
@@ -4289,6 +4529,11 @@
       <c r="D262" s="0">
         <v>175</v>
       </c>
+      <c r="E262" s="0" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="263">
       <c r="A263" s="0">
@@ -4305,6 +4550,11 @@
       <c r="D263" s="0">
         <v>176</v>
       </c>
+      <c r="E263" s="0" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="264">
       <c r="A264" s="0">
@@ -4321,6 +4571,11 @@
       <c r="D264" s="0">
         <v>177</v>
       </c>
+      <c r="E264" s="0" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="265">
       <c r="A265" s="0">
@@ -4337,6 +4592,11 @@
       <c r="D265" s="0">
         <v>178</v>
       </c>
+      <c r="E265" s="0" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="266">
       <c r="A266" s="0">
@@ -4353,6 +4613,11 @@
       <c r="D266" s="0">
         <v>168</v>
       </c>
+      <c r="E266" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="267">
       <c r="A267" s="0">
@@ -4369,6 +4634,11 @@
       <c r="D267" s="0">
         <v>169</v>
       </c>
+      <c r="E267" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="268">
       <c r="A268" s="0">
@@ -4384,6 +4654,11 @@
       </c>
       <c r="D268" s="0">
         <v>170</v>
+      </c>
+      <c r="E268" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row outlineLevel="0" r="269">
